--- a/artfynd/A 50431-2023 artfynd.xlsx
+++ b/artfynd/A 50431-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>115215768</v>
       </c>
       <c r="B2" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115215767</v>
+        <v>115215762</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462247</v>
+        <v>462391</v>
       </c>
       <c r="R3" t="n">
-        <v>7031709</v>
+        <v>7031544</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,12 +877,7 @@
         <v>115215763</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115215762</v>
+        <v>115215765</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462391</v>
+        <v>462445</v>
       </c>
       <c r="R5" t="n">
-        <v>7031544</v>
+        <v>7031563</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115215769</v>
+        <v>115215766</v>
       </c>
       <c r="B6" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462416</v>
+        <v>462446</v>
       </c>
       <c r="R6" t="n">
-        <v>7031581</v>
+        <v>7031598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115215770</v>
+        <v>115215767</v>
       </c>
       <c r="B7" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462255</v>
+        <v>462247</v>
       </c>
       <c r="R7" t="n">
-        <v>7031635</v>
+        <v>7031709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,6 +1253,11 @@
           <t>2024-03-15</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1299,220 +1279,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>115215766</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Långtjärnen Nordanälden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>462446</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7031598</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>115215765</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Långtjärnen Nordanälden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>462445</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7031563</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50431-2023 artfynd.xlsx
+++ b/artfynd/A 50431-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115215768</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115215762</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115215763</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115215765</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115215766</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,8 +1309,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115215767</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>